--- a/2026/Results/Regression_OLS_Results_2024.xlsx
+++ b/2026/Results/Regression_OLS_Results_2024.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1f12debbb769dbfe/Database/GRIP/2026/Results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_860DA7A0EF779EC949B9E62237AE5C34613639A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29C46F6C-8E7F-DF4F-A08C-3243D0CC420D}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="680" windowWidth="16100" windowHeight="9660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model_Summary" sheetId="1" r:id="rId1"/>
@@ -12,7 +18,7 @@
     <sheet name="VIF" sheetId="3" r:id="rId3"/>
     <sheet name="Residual_Tests" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -91,7 +97,7 @@
     <t>DF Model</t>
   </si>
   <si>
-    <t>sales_growth_volatility_win</t>
+    <t>ln_sales_growth_2019_2024_win</t>
   </si>
   <si>
     <t>OLS</t>
@@ -100,22 +106,22 @@
     <t>Least Squares</t>
   </si>
   <si>
-    <t>2026-03-13</t>
-  </si>
-  <si>
-    <t>18:36:23</t>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>09:53:36</t>
   </si>
   <si>
     <t>nonrobust</t>
   </si>
   <si>
-    <t>TARGET: WINSOR (percentile = 0.025)</t>
-  </si>
-  <si>
-    <t>92 companies winsorised</t>
-  </si>
-  <si>
-    <t>none (p=0.025)</t>
+    <t>TARGET: WINSOR (percentile = 0.01)</t>
+  </si>
+  <si>
+    <t>38 companies winsorised</t>
+  </si>
+  <si>
+    <t>none (p=0.01)</t>
   </si>
   <si>
     <t>0 observations affected</t>
@@ -223,8 +229,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -287,13 +293,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -331,7 +345,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -365,6 +379,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -399,9 +414,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -574,11 +590,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -586,7 +602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -594,7 +610,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -602,7 +618,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -610,7 +626,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -618,7 +634,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -626,23 +642,23 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
-        <v>1801</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -650,7 +666,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -658,7 +674,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -666,7 +682,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -674,7 +690,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -682,7 +698,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -690,79 +706,79 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
       <c r="B15">
-        <v>0.1448501536603382</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>0.102382131622813</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
       <c r="B16">
-        <v>0.1358285839321574</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>9.2917792278103484E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
       <c r="B17">
-        <v>16.05598116787461</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>10.817673362488179</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
       <c r="B18">
-        <v>5.655037262906505E-49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>2.6141098599610611E-31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19">
-        <v>614.0912489622458</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>-2952.7363387723722</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
       <c r="B20">
-        <v>-1188.182497924492</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>5945.4726775447434</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>21</v>
       </c>
       <c r="B21">
-        <v>-1078.03967632994</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>6055.6264791011417</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>7</v>
       </c>
       <c r="B22">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>1801</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -776,11 +792,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="27.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -803,477 +822,478 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>41</v>
       </c>
       <c r="B2">
-        <v>0.2735590551581141</v>
+        <v>-0.16436425203160629</v>
       </c>
       <c r="C2">
-        <v>0.01273053022647203</v>
+        <v>9.0177613617863958E-2</v>
       </c>
       <c r="D2">
-        <v>21.48842587791606</v>
+        <v>-1.822672450926847</v>
       </c>
       <c r="E2">
-        <v>2.278995082892709E-91</v>
+        <v>6.8518657083174034E-2</v>
       </c>
       <c r="F2">
-        <v>0.2485908947145599</v>
+        <v>-0.34122792109415723</v>
       </c>
       <c r="G2">
-        <v>0.2985272156016682</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>1.2499417030944541E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>42</v>
       </c>
       <c r="B3">
-        <v>-0.01456953103350234</v>
+        <v>6.1425149760102223E-2</v>
       </c>
       <c r="C3">
-        <v>0.004206716816464383</v>
+        <v>2.979235461780208E-2</v>
       </c>
       <c r="D3">
-        <v>-3.463397150119458</v>
+        <v>2.0617755980723431</v>
       </c>
       <c r="E3">
-        <v>0.0005458774883994897</v>
+        <v>3.9372218221777458E-2</v>
       </c>
       <c r="F3">
-        <v>-0.02282008922279685</v>
+        <v>2.9939611721476879E-3</v>
       </c>
       <c r="G3">
-        <v>-0.006318972844207843</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>0.1198563383480567</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>43</v>
       </c>
       <c r="B4">
-        <v>-0.004243143403790274</v>
+        <v>0.24284094137680229</v>
       </c>
       <c r="C4">
-        <v>0.004692816480610599</v>
+        <v>3.3234507053646757E-2</v>
       </c>
       <c r="D4">
-        <v>-0.9041784227705797</v>
+        <v>7.3068916287764178</v>
       </c>
       <c r="E4">
-        <v>0.3660217262657344</v>
+        <v>4.087969184684621E-13</v>
       </c>
       <c r="F4">
-        <v>-0.01344708013977897</v>
+        <v>0.17765872351615161</v>
       </c>
       <c r="G4">
-        <v>0.004960793332198426</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>0.30802315923745299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>44</v>
       </c>
       <c r="B5">
-        <v>0.007912885565166497</v>
+        <v>0.10666045812833699</v>
       </c>
       <c r="C5">
-        <v>0.004706352001960692</v>
+        <v>3.3330232956239339E-2</v>
       </c>
       <c r="D5">
-        <v>1.681320386122828</v>
+        <v>3.2001113904117018</v>
       </c>
       <c r="E5">
-        <v>0.09287408173703708</v>
+        <v>1.397651077574691E-3</v>
       </c>
       <c r="F5">
-        <v>-0.001317598145908405</v>
+        <v>4.129049484310017E-2</v>
       </c>
       <c r="G5">
-        <v>0.0171433692762414</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>0.1720304214135738</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>45</v>
       </c>
       <c r="B6">
-        <v>0.009042443254684517</v>
+        <v>-0.14536467202595971</v>
       </c>
       <c r="C6">
-        <v>0.004529019735752851</v>
+        <v>3.2068213841293533E-2</v>
       </c>
       <c r="D6">
-        <v>1.996556381351561</v>
+        <v>-4.5329831198386481</v>
       </c>
       <c r="E6">
-        <v>0.04602368613195008</v>
+        <v>6.1981857175670682E-6</v>
       </c>
       <c r="F6">
-        <v>0.0001597581345347196</v>
+        <v>-0.20825946079568711</v>
       </c>
       <c r="G6">
-        <v>0.01792512837483431</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>-8.246988325623221E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>46</v>
       </c>
       <c r="B7">
-        <v>-0.02553228985279005</v>
+        <v>-7.5492046937248591E-2</v>
       </c>
       <c r="C7">
-        <v>0.008618020961351546</v>
+        <v>6.1012640050427343E-2</v>
       </c>
       <c r="D7">
-        <v>-2.962662769943631</v>
+        <v>-1.2373181503841491</v>
       </c>
       <c r="E7">
-        <v>0.003089878217596284</v>
+        <v>0.216130199029162</v>
       </c>
       <c r="F7">
-        <v>-0.04243465968664802</v>
+        <v>-0.19515499814639059</v>
       </c>
       <c r="G7">
-        <v>-0.00862992001893207</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>4.4170904271893442E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>47</v>
       </c>
       <c r="B8">
-        <v>0.08980072515034389</v>
+        <v>3.3736039675073867E-2</v>
       </c>
       <c r="C8">
-        <v>0.02641155610311293</v>
+        <v>0.1870957662800069</v>
       </c>
       <c r="D8">
-        <v>3.400054309551255</v>
+        <v>0.18031428688014581</v>
       </c>
       <c r="E8">
-        <v>0.0006884294223721315</v>
+        <v>0.85692611515247552</v>
       </c>
       <c r="F8">
-        <v>0.03800021420420981</v>
+        <v>-0.33321139176367931</v>
       </c>
       <c r="G8">
-        <v>0.141601236096478</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>0.40068347111382702</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>48</v>
       </c>
       <c r="B9">
-        <v>0.2867007000179302</v>
+        <v>0.31281534015722268</v>
       </c>
       <c r="C9">
-        <v>0.03413325427233597</v>
+        <v>0.2417969344055162</v>
       </c>
       <c r="D9">
-        <v>8.399454025990513</v>
+        <v>1.2937109435498551</v>
       </c>
       <c r="E9">
-        <v>8.965226195055561E-17</v>
+        <v>0.1959310794492754</v>
       </c>
       <c r="F9">
-        <v>0.2197557610427927</v>
+        <v>-0.16141647050321009</v>
       </c>
       <c r="G9">
-        <v>0.3536456389930678</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>0.78704715081765553</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>49</v>
       </c>
       <c r="B10">
-        <v>0.1117982824324015</v>
+        <v>-2.0534217393787961E-2</v>
       </c>
       <c r="C10">
-        <v>0.03196905832564928</v>
+        <v>0.22646505567449449</v>
       </c>
       <c r="D10">
-        <v>3.497077746037454</v>
+        <v>-9.0672785400068304E-2</v>
       </c>
       <c r="E10">
-        <v>0.0004817956192553695</v>
+        <v>0.92776267290002978</v>
       </c>
       <c r="F10">
-        <v>0.04909794212415998</v>
+        <v>-0.46469590069998112</v>
       </c>
       <c r="G10">
-        <v>0.174498622740643</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>0.42362746591240519</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>50</v>
       </c>
       <c r="B11">
-        <v>-0.06533888787945047</v>
+        <v>0.25888225417059779</v>
       </c>
       <c r="C11">
-        <v>0.02376481434871504</v>
+        <v>0.16834642237546049</v>
       </c>
       <c r="D11">
-        <v>-2.749396099657868</v>
+        <v>1.5377948073836489</v>
       </c>
       <c r="E11">
-        <v>0.006030164993992701</v>
+        <v>0.1242743551382692</v>
       </c>
       <c r="F11">
-        <v>-0.1119483917268351</v>
+        <v>-7.1292439307647337E-2</v>
       </c>
       <c r="G11">
-        <v>-0.01872938403206583</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>0.58905694764884298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>51</v>
       </c>
       <c r="B12">
-        <v>-0.02936605035859687</v>
+        <v>-8.8400358687323825E-3</v>
       </c>
       <c r="C12">
-        <v>0.01757428705305052</v>
+        <v>0.1244946047575522</v>
       </c>
       <c r="D12">
-        <v>-1.670966809063219</v>
+        <v>-7.1007381291325583E-2</v>
       </c>
       <c r="E12">
-        <v>0.09490197296047674</v>
+        <v>0.94339976020568161</v>
       </c>
       <c r="F12">
-        <v>-0.06383418412958466</v>
+        <v>-0.25300897860898419</v>
       </c>
       <c r="G12">
-        <v>0.005102083412390931</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>0.23532890687151939</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>52</v>
       </c>
       <c r="B13">
-        <v>-0.08864128739415007</v>
+        <v>0.29739178388837328</v>
       </c>
       <c r="C13">
-        <v>0.02080676921223907</v>
+        <v>0.14739327646773079</v>
       </c>
       <c r="D13">
-        <v>-4.260213899138604</v>
+        <v>2.017675371735713</v>
       </c>
       <c r="E13">
-        <v>2.147750808399283E-05</v>
+        <v>4.3773055789452398E-2</v>
       </c>
       <c r="F13">
-        <v>-0.1294492304068393</v>
+        <v>8.3121040722544115E-3</v>
       </c>
       <c r="G13">
-        <v>-0.0478333443814609</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>0.58647146370449232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>53</v>
       </c>
       <c r="B14">
-        <v>-0.01060100326591948</v>
+        <v>0.40906705298437729</v>
       </c>
       <c r="C14">
-        <v>0.01732705266287508</v>
+        <v>0.12274252525629489</v>
       </c>
       <c r="D14">
-        <v>-0.6118180323092788</v>
+        <v>3.3327247596561751</v>
       </c>
       <c r="E14">
-        <v>0.540735381818567</v>
+        <v>8.7740724354289426E-4</v>
       </c>
       <c r="F14">
-        <v>-0.04458424066485919</v>
+        <v>0.16833443104093421</v>
       </c>
       <c r="G14">
-        <v>0.02338223413302024</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>0.64979967492782031</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>54</v>
       </c>
       <c r="B15">
-        <v>-0.1182392760610441</v>
+        <v>0.47726335649151852</v>
       </c>
       <c r="C15">
-        <v>0.02283250404700134</v>
+        <v>0.1617428572991991</v>
       </c>
       <c r="D15">
-        <v>-5.178550535571802</v>
+        <v>2.9507538351981482</v>
       </c>
       <c r="E15">
-        <v>2.486548335614834E-07</v>
+        <v>3.2109111204504698E-3</v>
       </c>
       <c r="F15">
-        <v>-0.1630202564469345</v>
+        <v>0.16004011184213829</v>
       </c>
       <c r="G15">
-        <v>-0.07345829567515375</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>0.79448660114089864</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>55</v>
       </c>
       <c r="B16">
-        <v>0.1529883943641761</v>
+        <v>-0.44905694170045912</v>
       </c>
       <c r="C16">
-        <v>0.02439739580092749</v>
+        <v>0.17282897469627009</v>
       </c>
       <c r="D16">
-        <v>6.270685429399808</v>
+        <v>-2.5982734809925971</v>
       </c>
       <c r="E16">
-        <v>4.489210918958535E-10</v>
+        <v>9.4457563493464802E-3</v>
       </c>
       <c r="F16">
-        <v>0.1051382198682419</v>
+        <v>-0.7880231813110159</v>
       </c>
       <c r="G16">
-        <v>0.2008385688601103</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>-0.1100907020899022</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>56</v>
       </c>
       <c r="B17">
-        <v>-0.02483360290702336</v>
+        <v>0.29232217392146898</v>
       </c>
       <c r="C17">
-        <v>0.01568471153608212</v>
+        <v>0.1111072737518259</v>
       </c>
       <c r="D17">
-        <v>-1.58329994465595</v>
+        <v>2.6309904297932158</v>
       </c>
       <c r="E17">
-        <v>0.1135286882701325</v>
+        <v>8.5862130141071292E-3</v>
       </c>
       <c r="F17">
-        <v>-0.0555957461309895</v>
+        <v>7.4409553406166312E-2</v>
       </c>
       <c r="G17">
-        <v>0.005928540316942784</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>0.51023479443677178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>57</v>
       </c>
       <c r="B18">
-        <v>0.009479110539369373</v>
+        <v>0.33745645086159293</v>
       </c>
       <c r="C18">
-        <v>0.02109570698462114</v>
+        <v>0.14943993342118569</v>
       </c>
       <c r="D18">
-        <v>0.4493383675778054</v>
+        <v>2.2581410680269518</v>
       </c>
       <c r="E18">
-        <v>0.6532416510858976</v>
+        <v>2.40560394364265E-2</v>
       </c>
       <c r="F18">
-        <v>-0.03189552094039066</v>
+        <v>4.4362700994404092E-2</v>
       </c>
       <c r="G18">
-        <v>0.05085374201912941</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>0.63055020072878176</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>58</v>
       </c>
       <c r="B19">
-        <v>0.02150662804654589</v>
+        <v>5.7586084706045398E-2</v>
       </c>
       <c r="C19">
-        <v>0.02048091728303745</v>
+        <v>0.1450849945041478</v>
       </c>
       <c r="D19">
-        <v>1.050081290272968</v>
+        <v>0.39691275381617142</v>
       </c>
       <c r="E19">
-        <v>0.2938216223046264</v>
+        <v>0.69147880051877708</v>
       </c>
       <c r="F19">
-        <v>-0.01866222742584352</v>
+        <v>-0.22696640481381891</v>
       </c>
       <c r="G19">
-        <v>0.06167548351893531</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>0.34213857422590971</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>59</v>
       </c>
       <c r="B20">
-        <v>-0.0658435886410936</v>
+        <v>0.38498536534579492</v>
       </c>
       <c r="C20">
-        <v>0.01733406814433043</v>
+        <v>0.1226141555858111</v>
       </c>
       <c r="D20">
-        <v>-3.79850754553711</v>
+        <v>3.1398117412011541</v>
       </c>
       <c r="E20">
-        <v>0.0001504008590392517</v>
+        <v>1.7179828782516371E-3</v>
       </c>
       <c r="F20">
-        <v>-0.09984058537789671</v>
+        <v>0.14450451243911419</v>
       </c>
       <c r="G20">
-        <v>-0.0318465919042905</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>0.6254662182524755</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>60</v>
       </c>
       <c r="B21">
-        <v>-0.002125472856292568</v>
+        <v>0.27311335865947839</v>
       </c>
       <c r="C21">
-        <v>0.008518574752531545</v>
+        <v>6.0328016514735718E-2</v>
       </c>
       <c r="D21">
-        <v>-0.2495103838421939</v>
+        <v>4.5271397012160639</v>
       </c>
       <c r="E21">
-        <v>0.8029944630816738</v>
+        <v>6.3700180434180484E-6</v>
       </c>
       <c r="F21">
-        <v>-0.0188328006256686</v>
+        <v>0.15479314680205741</v>
       </c>
       <c r="G21">
-        <v>0.01458185491308346</v>
+        <v>0.39143357051689948</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -1281,164 +1301,164 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>41</v>
       </c>
       <c r="B2">
-        <v>9.785727525021919</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>9.7901611944396105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>42</v>
       </c>
       <c r="B3">
-        <v>1.06852992510659</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>1.068567652844101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>43</v>
       </c>
       <c r="B4">
-        <v>1.329741662351603</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>1.3297526023699311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>44</v>
       </c>
       <c r="B5">
-        <v>1.337423489964881</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>1.3374238513027179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>45</v>
       </c>
       <c r="B6">
-        <v>1.23853578913024</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>1.2380606139563</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>46</v>
       </c>
       <c r="B7">
-        <v>1.119123543238465</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>1.118447779973639</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>47</v>
       </c>
       <c r="B8">
-        <v>1.23373421866502</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>1.2337375406282269</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>48</v>
       </c>
       <c r="B9">
-        <v>1.139862523752213</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>1.1398729861138881</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>49</v>
       </c>
       <c r="B10">
-        <v>1.163293843028975</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>1.163297016422582</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>50</v>
       </c>
       <c r="B11">
-        <v>1.329455237294773</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>1.3294639069826839</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>51</v>
       </c>
       <c r="B12">
-        <v>1.669391112600822</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>1.6694900613020229</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>52</v>
       </c>
       <c r="B13">
-        <v>1.420352451852149</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>1.4203996641724039</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>53</v>
       </c>
       <c r="B14">
-        <v>1.902802578236048</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>1.902919862372678</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>54</v>
       </c>
       <c r="B15">
-        <v>1.32213586825728</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>1.322159896637376</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>55</v>
       </c>
       <c r="B16">
-        <v>1.273712990275683</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>1.273739600133049</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>56</v>
       </c>
       <c r="B17">
-        <v>2.331286440388919</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>2.3315195976067731</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>57</v>
       </c>
       <c r="B18">
-        <v>1.394598783757324</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>1.3946399400291349</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>58</v>
       </c>
       <c r="B19">
-        <v>1.413058586069632</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>1.413107459215287</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>59</v>
       </c>
       <c r="B20">
-        <v>1.750384636720423</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>1.753186262299911</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>60</v>
       </c>
       <c r="B21">
-        <v>1.046439385109044</v>
+        <v>1.046230150651523</v>
       </c>
     </row>
   </sheetData>
@@ -1447,11 +1467,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
@@ -1462,23 +1482,23 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>65</v>
       </c>
       <c r="B2">
-        <v>0.8444803953170776</v>
+        <v>0.45084559917449951</v>
       </c>
       <c r="C2">
-        <v>5.393812187851263E-39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>66</v>
       </c>
       <c r="B3">
-        <v>2268.498767190867</v>
+        <v>151302.362864166</v>
       </c>
       <c r="C3">
         <v>0</v>
